--- a/docs/StructureDefinition-VAERSImmunization-pvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-pvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file ADERS (undefined) to us-core-immunization</t>
+    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -237,7 +237,7 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+    <t>Mapping: VA Adverse Drug Event Reporting System (VA ADERS)</t>
   </si>
   <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
@@ -675,7 +675,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1927: source value from ADERS - 22_PVac2_TypeBrand</t>
+    <t>1927: source value from ADERS - 22_PVac2_TypeBrand (A-22.21)</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -783,7 +783,7 @@
 </t>
   </si>
   <si>
-    <t>1933: source value from ADERS - 22_PVac2_Date</t>
+    <t>1933: source value from ADERS - 22_PVac2_Date (A-22.27)</t>
   </si>
   <si>
     <t>Immunization.recorded</t>
@@ -977,7 +977,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1928: source value from ADERS - 22_PVac2_Mfgr</t>
+    <t>1928: source value from ADERS - 22_PVac2_Mfgr (A-22.22)</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -989,7 +989,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1929: source value from ADERS - 22_PVac2_Lot</t>
+    <t>1929: source value from ADERS - 22_PVac2_Lot (A-22.23)</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -1035,7 +1035,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1931: source value from ADERS - 22_PVac2_Site</t>
+    <t>1931: source value from ADERS - 22_PVac2_Site (A-22.25)</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1062,7 +1062,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-route</t>
   </si>
   <si>
-    <t>1930: source value from ADERS - 22_PVac2_Route</t>
+    <t>1930: source value from ADERS - 22_PVac2_Route (A-22.24)</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1519,7 +1519,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1932: source value from ADERS - 22_PVac2_DoseInSeries</t>
+    <t>1932: source value from ADERS - 22_PVac2_DoseInSeries (A-22.26)</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>
@@ -1883,7 +1883,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="67.44921875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="147.5546875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VAERSImmunization-pvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-pvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunization-pvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-pvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunization-pvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-pvac2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2971" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2973" uniqueCount="490">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization</t>
+    <t>This StructureDefinition contains the maps for ADERS to Immunization</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-immunization</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Immunization</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -274,11 +274,11 @@
     <t>Immunization event information</t>
   </si>
   <si>
-    <t>\-</t>
+    <t>Describes the event of a patient being administered a vaccine or a record of an immunization as reported by a patient, a clinician or another party.</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}us-core-5:SHOULD have a translation to the NDC value set {vaccineCode.coding.where(system='http://hl7.org/fhir/sid/ndc').empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -517,7 +517,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-status</t>
+    <t>A set of codes indicating the current status of an Immunization.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/immunization-status|4.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -548,6 +551,9 @@
     <t>example</t>
   </si>
   <si>
+    <t>The reason why a vaccine was not administered.</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/immunization-status-reason</t>
   </si>
   <si>
@@ -560,20 +566,16 @@
     <t>Immunization.vaccineCode</t>
   </si>
   <si>
-    <t>Vaccine Product Type (bind to CVX)</t>
+    <t>Vaccine product administered</t>
   </si>
   <si>
     <t>Vaccine that was administered or was to be administered.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1010.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">us-core-5
-</t>
+    <t>The code for vaccine product administered.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/vaccine-code</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -675,7 +677,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1927: source value from ADERS - 22_PVac2_TypeBrand (A-22.21)</t>
+    <t>1927: source value from ADERS - PVac2_TypeBrand (A-22.21)</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -687,11 +689,7 @@
     <t>Immunization.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Patient
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(Patient)
 </t>
   </si>
   <si>
@@ -783,7 +781,7 @@
 </t>
   </si>
   <si>
-    <t>1933: source value from ADERS - 22_PVac2_Date (A-22.27)</t>
+    <t>1933: source value from ADERS - PVac2_Date (A-22.27)</t>
   </si>
   <si>
     <t>Immunization.recorded</t>
@@ -930,6 +928,9 @@
   </si>
   <si>
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
@@ -977,7 +978,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1928: source value from ADERS - 22_PVac2_Mfgr (A-22.22)</t>
+    <t>1928: source value from ADERS - PVac2_Mfgr (A-22.22)</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -989,7 +990,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1929: source value from ADERS - 22_PVac2_Lot (A-22.23)</t>
+    <t>1929: source value from ADERS - PVac2_Lot (A-22.23)</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -1035,7 +1036,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1931: source value from ADERS - 22_PVac2_Site (A-22.25)</t>
+    <t>1931: source value from ADERS - PVac2_Site (A-22.25)</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1062,7 +1063,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-route</t>
   </si>
   <si>
-    <t>1930: source value from ADERS - 22_PVac2_Route (A-22.24)</t>
+    <t>1930: source value from ADERS - PVac2_Route (A-22.24)</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1519,7 +1520,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1932: source value from ADERS - 22_PVac2_DoseInSeries (A-22.26)</t>
+    <t>1932: source value from ADERS - PVac2_DoseInSeries (A-22.26)</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>
@@ -1858,7 +1859,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="67.61328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="50.07421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1873,7 +1874,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="66.7265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.8515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.24609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -2059,9 +2060,7 @@
       <c r="M2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="N2" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
         <v>80</v>
@@ -3270,7 +3269,7 @@
         <v>91</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>92</v>
@@ -3316,9 +3315,11 @@
       <c r="X12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="Y12" s="2"/>
+      <c r="Y12" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="Z12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3357,16 +3358,16 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>80</v>
@@ -3374,10 +3375,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3391,7 +3392,7 @@
         <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>80</v>
@@ -3400,16 +3401,16 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3435,11 +3436,13 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="Y13" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="Z13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
@@ -3457,7 +3460,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3478,13 +3481,13 @@
         <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>80</v>
@@ -3495,10 +3498,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3512,7 +3515,7 @@
         <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>80</v>
@@ -3521,13 +3524,13 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3554,11 +3557,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3576,7 +3581,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>91</v>
@@ -3585,7 +3590,7 @@
         <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>103</v>
@@ -3597,27 +3602,27 @@
         <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3640,13 +3645,13 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3697,7 +3702,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3724,7 +3729,7 @@
         <v>80</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>80</v>
@@ -3735,10 +3740,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3767,7 +3772,7 @@
         <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>140</v>
@@ -3808,19 +3813,19 @@
         <v>80</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3847,7 +3852,7 @@
         <v>80</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>80</v>
@@ -3858,10 +3863,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3884,19 +3889,19 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -3945,7 +3950,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -3969,10 +3974,10 @@
         <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>80</v>
@@ -3983,10 +3988,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4009,19 +4014,19 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -4070,7 +4075,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4085,7 +4090,7 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>80</v>
@@ -4094,10 +4099,10 @@
         <v>80</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>80</v>
@@ -4108,14 +4113,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>216</v>
+        <v>80</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4125,7 +4130,7 @@
         <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>80</v>
@@ -4191,7 +4196,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>91</v>
@@ -4367,7 +4372,7 @@
         <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>80</v>
@@ -4430,7 +4435,7 @@
         <v>80</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>232</v>
@@ -4728,13 +4733,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>80</v>
@@ -4866,7 +4871,7 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>261</v>
@@ -4901,7 +4906,7 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y25" t="s" s="2">
         <v>264</v>
@@ -5231,13 +5236,13 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5288,7 +5293,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5315,7 +5320,7 @@
         <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>80</v>
@@ -5358,7 +5363,7 @@
         <v>138</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>140</v>
@@ -5399,19 +5404,19 @@
         <v>80</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5438,7 +5443,7 @@
         <v>80</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>80</v>
@@ -5475,7 +5480,7 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>285</v>
@@ -5633,13 +5638,13 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>177</v>
+        <v>294</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5657,7 +5662,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5695,10 +5700,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5724,13 +5729,13 @@
         <v>149</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5780,7 +5785,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5807,7 +5812,7 @@
         <v>80</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
@@ -5818,10 +5823,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5844,16 +5849,16 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5903,7 +5908,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5918,7 +5923,7 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>80</v>
@@ -5941,10 +5946,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5967,13 +5972,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6024,7 +6029,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6039,7 +6044,7 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>80</v>
@@ -6048,24 +6053,24 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6088,13 +6093,13 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6145,7 +6150,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6169,10 +6174,10 @@
         <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>80</v>
@@ -6183,10 +6188,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6209,13 +6214,13 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6242,13 +6247,13 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
@@ -6266,7 +6271,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6281,7 +6286,7 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>80</v>
@@ -6290,24 +6295,24 @@
         <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6330,13 +6335,13 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6363,13 +6368,13 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6387,7 +6392,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6402,7 +6407,7 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>80</v>
@@ -6411,24 +6416,24 @@
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6451,13 +6456,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6508,7 +6513,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6532,10 +6537,10 @@
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>80</v>
@@ -6546,10 +6551,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6572,13 +6577,13 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6629,7 +6634,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6650,13 +6655,13 @@
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -6667,10 +6672,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6693,13 +6698,13 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6750,7 +6755,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6777,7 +6782,7 @@
         <v>80</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>80</v>
@@ -6788,10 +6793,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6820,7 +6825,7 @@
         <v>138</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>140</v>
@@ -6873,7 +6878,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6900,7 +6905,7 @@
         <v>80</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6911,14 +6916,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6940,10 +6945,10 @@
         <v>137</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>140</v>
@@ -6998,7 +7003,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7036,10 +7041,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7062,13 +7067,13 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7095,13 +7100,13 @@
         <v>80</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>177</v>
+        <v>294</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>80</v>
@@ -7119,7 +7124,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7140,13 +7145,13 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
@@ -7157,10 +7162,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7183,16 +7188,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7242,7 +7247,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>91</v>
@@ -7263,16 +7268,16 @@
         <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>80</v>
@@ -7280,10 +7285,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7306,13 +7311,13 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7363,7 +7368,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7384,13 +7389,13 @@
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
@@ -7401,10 +7406,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7427,13 +7432,13 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7460,13 +7465,13 @@
         <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
@@ -7484,7 +7489,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7505,13 +7510,13 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>80</v>
@@ -7522,10 +7527,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7548,13 +7553,13 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7605,7 +7610,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7626,7 +7631,7 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -7643,10 +7648,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7672,20 +7677,20 @@
         <v>253</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q48" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="R48" t="s" s="2">
         <v>80</v>
@@ -7730,7 +7735,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7754,7 +7759,7 @@
         <v>80</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>134</v>
@@ -7768,10 +7773,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7794,13 +7799,13 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7827,13 +7832,13 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -7851,7 +7856,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7889,10 +7894,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7915,13 +7920,13 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7972,7 +7977,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7984,7 +7989,7 @@
         <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>80</v>
@@ -8010,10 +8015,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8036,13 +8041,13 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8093,7 +8098,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8120,7 +8125,7 @@
         <v>80</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>80</v>
@@ -8131,10 +8136,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8163,7 +8168,7 @@
         <v>138</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>140</v>
@@ -8216,7 +8221,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8243,7 +8248,7 @@
         <v>80</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>80</v>
@@ -8254,14 +8259,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8283,10 +8288,10 @@
         <v>137</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>140</v>
@@ -8341,7 +8346,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8379,10 +8384,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8405,13 +8410,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8462,7 +8467,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8486,7 +8491,7 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>134</v>
@@ -8500,10 +8505,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8529,10 +8534,10 @@
         <v>105</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8583,7 +8588,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8621,10 +8626,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8650,10 +8655,10 @@
         <v>245</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8704,7 +8709,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8728,7 +8733,7 @@
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>134</v>
@@ -8742,10 +8747,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8771,10 +8776,10 @@
         <v>245</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8825,7 +8830,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8849,7 +8854,7 @@
         <v>80</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>134</v>
@@ -8863,10 +8868,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8889,13 +8894,13 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8922,13 +8927,13 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -8946,7 +8951,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8970,7 +8975,7 @@
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>134</v>
@@ -8984,10 +8989,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9010,13 +9015,13 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9043,13 +9048,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9067,7 +9072,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9105,10 +9110,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9131,16 +9136,16 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9190,7 +9195,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9214,10 +9219,10 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
@@ -9228,10 +9233,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9254,13 +9259,13 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9311,7 +9316,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9338,7 +9343,7 @@
         <v>80</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9349,10 +9354,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9381,7 +9386,7 @@
         <v>138</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>140</v>
@@ -9434,7 +9439,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9461,7 +9466,7 @@
         <v>80</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9472,14 +9477,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9501,10 +9506,10 @@
         <v>137</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>140</v>
@@ -9559,7 +9564,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9597,10 +9602,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9626,10 +9631,10 @@
         <v>245</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9680,7 +9685,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9704,7 +9709,7 @@
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>240</v>
@@ -9718,10 +9723,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9744,13 +9749,13 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9801,7 +9806,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9825,10 +9830,10 @@
         <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -9839,10 +9844,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9868,10 +9873,10 @@
         <v>253</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9922,7 +9927,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9946,10 +9951,10 @@
         <v>80</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -9960,10 +9965,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9986,13 +9991,13 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10043,7 +10048,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10081,10 +10086,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10107,13 +10112,13 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10164,7 +10169,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10191,7 +10196,7 @@
         <v>80</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>80</v>
@@ -10202,10 +10207,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10234,7 +10239,7 @@
         <v>138</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -10287,7 +10292,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10314,7 +10319,7 @@
         <v>80</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>80</v>
@@ -10325,14 +10330,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10354,10 +10359,10 @@
         <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>140</v>
@@ -10412,7 +10417,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10450,10 +10455,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10476,13 +10481,13 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10533,7 +10538,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10571,10 +10576,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10600,10 +10605,10 @@
         <v>276</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10654,7 +10659,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10692,10 +10697,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10718,13 +10723,13 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10751,13 +10756,13 @@
         <v>80</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
@@ -10775,7 +10780,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10813,10 +10818,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10839,16 +10844,16 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10893,10 +10898,10 @@
         <v>80</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>91</v>
@@ -10934,13 +10939,13 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>80</v>
@@ -10962,16 +10967,16 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11021,7 +11026,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>91</v>
@@ -11036,7 +11041,7 @@
         <v>103</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>80</v>
@@ -11059,10 +11064,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11085,16 +11090,16 @@
         <v>80</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11144,7 +11149,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-VAERSImmunization-pvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-pvac2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2973" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2971" uniqueCount="489">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for ADERS to Immunization</t>
+    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Immunization</t>
+    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-immunization</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -274,11 +274,11 @@
     <t>Immunization event information</t>
   </si>
   <si>
-    <t>Describes the event of a patient being administered a vaccine or a record of an immunization as reported by a patient, a clinician or another party.</t>
+    <t>\-</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}us-core-5:SHOULD have a translation to the NDC value set {vaccineCode.coding.where(system='http://hl7.org/fhir/sid/ndc').empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -517,10 +517,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>A set of codes indicating the current status of an Immunization.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-status</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -551,9 +548,6 @@
     <t>example</t>
   </si>
   <si>
-    <t>The reason why a vaccine was not administered.</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/immunization-status-reason</t>
   </si>
   <si>
@@ -566,16 +560,20 @@
     <t>Immunization.vaccineCode</t>
   </si>
   <si>
-    <t>Vaccine product administered</t>
+    <t>Vaccine Product Type (bind to CVX)</t>
   </si>
   <si>
     <t>Vaccine that was administered or was to be administered.</t>
   </si>
   <si>
-    <t>The code for vaccine product administered.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/vaccine-code</t>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1010.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">us-core-5
+</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -677,7 +675,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1927: source value from ADERS - PVac2_TypeBrand (A-22.21)</t>
+    <t>1927: source value from ADERS - 22_PVac2_TypeBrand</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -689,7 +687,11 @@
     <t>Immunization.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Patient
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>
@@ -781,7 +783,7 @@
 </t>
   </si>
   <si>
-    <t>1933: source value from ADERS - PVac2_Date (A-22.27)</t>
+    <t>1933: source value from ADERS - 22_PVac2_Date</t>
   </si>
   <si>
     <t>Immunization.recorded</t>
@@ -928,9 +930,6 @@
   </si>
   <si>
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
@@ -978,7 +977,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1928: source value from ADERS - PVac2_Mfgr (A-22.22)</t>
+    <t>1928: source value from ADERS - 22_PVac2_Mfgr</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -990,7 +989,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1929: source value from ADERS - PVac2_Lot (A-22.23)</t>
+    <t>1929: source value from ADERS - 22_PVac2_Lot</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -1036,7 +1035,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1931: source value from ADERS - PVac2_Site (A-22.25)</t>
+    <t>1931: source value from ADERS - 22_PVac2_Site</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1063,7 +1062,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-route</t>
   </si>
   <si>
-    <t>1930: source value from ADERS - PVac2_Route (A-22.24)</t>
+    <t>1930: source value from ADERS - 22_PVac2_Route</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1520,7 +1519,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1932: source value from ADERS - PVac2_DoseInSeries (A-22.26)</t>
+    <t>1932: source value from ADERS - 22_PVac2_DoseInSeries</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>
@@ -1859,7 +1858,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="50.07421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="67.61328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1874,7 +1873,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="66.7265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.24609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.8515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -2060,7 +2059,9 @@
       <c r="M2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="N2" s="2"/>
+      <c r="N2" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
         <v>80</v>
@@ -3269,7 +3270,7 @@
         <v>91</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>92</v>
@@ -3315,11 +3316,9 @@
       <c r="X12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Y12" s="2"/>
+      <c r="Z12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3358,16 +3357,16 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AN12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AN12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO12" t="s" s="2">
+      <c r="AP12" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>80</v>
@@ -3375,10 +3374,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3392,7 +3391,7 @@
         <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>80</v>
@@ -3401,16 +3400,16 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3436,14 +3435,12 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y13" s="2"/>
+      <c r="Z13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="Y13" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
       </c>
@@ -3460,7 +3457,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3481,13 +3478,13 @@
         <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>80</v>
@@ -3498,10 +3495,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3515,7 +3512,7 @@
         <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>80</v>
@@ -3524,13 +3521,13 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3557,13 +3554,11 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3581,7 +3576,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>91</v>
@@ -3590,7 +3585,7 @@
         <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>103</v>
@@ -3602,27 +3597,27 @@
         <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AO14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AP14" t="s" s="2">
+      <c r="AQ14" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AQ14" t="s" s="2">
-        <v>185</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3645,13 +3640,13 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3702,7 +3697,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3729,7 +3724,7 @@
         <v>80</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>80</v>
@@ -3740,10 +3735,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3772,7 +3767,7 @@
         <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>140</v>
@@ -3813,19 +3808,19 @@
         <v>80</v>
       </c>
       <c r="AB16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AC16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AC16" t="s" s="2">
+      <c r="AD16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AD16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE16" t="s" s="2">
+      <c r="AF16" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3852,7 +3847,7 @@
         <v>80</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>80</v>
@@ -3863,10 +3858,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3889,19 +3884,19 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -3950,7 +3945,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -3974,10 +3969,10 @@
         <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>80</v>
@@ -3988,10 +3983,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4014,19 +4009,19 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -4075,7 +4070,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4090,19 +4085,19 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>80</v>
@@ -4113,14 +4108,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4130,7 +4125,7 @@
         <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>80</v>
@@ -4196,7 +4191,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>91</v>
@@ -4372,7 +4367,7 @@
         <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>80</v>
@@ -4435,7 +4430,7 @@
         <v>80</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>232</v>
@@ -4733,13 +4728,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>80</v>
@@ -4871,7 +4866,7 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>261</v>
@@ -4906,7 +4901,7 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y25" t="s" s="2">
         <v>264</v>
@@ -5236,13 +5231,13 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5293,7 +5288,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5320,7 +5315,7 @@
         <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>80</v>
@@ -5363,7 +5358,7 @@
         <v>138</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>140</v>
@@ -5404,19 +5399,19 @@
         <v>80</v>
       </c>
       <c r="AB29" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AC29" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AC29" t="s" s="2">
+      <c r="AD29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE29" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AD29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE29" t="s" s="2">
+      <c r="AF29" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5443,7 +5438,7 @@
         <v>80</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>80</v>
@@ -5480,7 +5475,7 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>285</v>
@@ -5638,31 +5633,31 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y31" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="Y31" t="s" s="2">
+      <c r="Z31" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="Z31" t="s" s="2">
+      <c r="AA31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5700,10 +5695,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5729,13 +5724,13 @@
         <v>149</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5785,7 +5780,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5812,7 +5807,7 @@
         <v>80</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
@@ -5823,10 +5818,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5849,16 +5844,16 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5908,7 +5903,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5923,7 +5918,7 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>80</v>
@@ -5946,10 +5941,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5972,13 +5967,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6029,7 +6024,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6044,33 +6039,33 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ34" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>316</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6093,13 +6088,13 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6150,7 +6145,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6174,10 +6169,10 @@
         <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>80</v>
@@ -6188,10 +6183,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6214,13 +6209,13 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6247,14 +6242,14 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>327</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
       </c>
@@ -6271,7 +6266,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6286,33 +6281,33 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AL36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AO36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ36" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ36" t="s" s="2">
-        <v>331</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6335,13 +6330,13 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6368,14 +6363,14 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>336</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
       </c>
@@ -6392,7 +6387,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6407,33 +6402,33 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AL37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AO37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ37" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>340</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6456,13 +6451,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6513,7 +6508,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6537,10 +6532,10 @@
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>80</v>
@@ -6551,10 +6546,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6577,13 +6572,13 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6634,7 +6629,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6655,13 +6650,13 @@
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -6672,10 +6667,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6698,13 +6693,13 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6755,7 +6750,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6782,7 +6777,7 @@
         <v>80</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>80</v>
@@ -6793,10 +6788,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6825,7 +6820,7 @@
         <v>138</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>140</v>
@@ -6878,7 +6873,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6905,7 +6900,7 @@
         <v>80</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6916,14 +6911,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6945,10 +6940,10 @@
         <v>137</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>140</v>
@@ -7003,7 +6998,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7041,10 +7036,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7067,13 +7062,13 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7100,14 +7095,14 @@
         <v>80</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>294</v>
+        <v>177</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>365</v>
-      </c>
       <c r="AA43" t="s" s="2">
         <v>80</v>
       </c>
@@ -7124,7 +7119,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7145,13 +7140,13 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
@@ -7162,10 +7157,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7188,16 +7183,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7247,7 +7242,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>91</v>
@@ -7268,16 +7263,16 @@
         <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="AN44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>80</v>
@@ -7285,10 +7280,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7311,13 +7306,13 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7368,7 +7363,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7389,13 +7384,13 @@
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
@@ -7406,10 +7401,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7432,13 +7427,13 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7465,14 +7460,14 @@
         <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>387</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
       </c>
@@ -7489,7 +7484,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7510,13 +7505,13 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>80</v>
@@ -7527,10 +7522,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7553,13 +7548,13 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7610,7 +7605,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7631,7 +7626,7 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -7648,10 +7643,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7677,20 +7672,20 @@
         <v>253</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q48" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="R48" t="s" s="2">
         <v>80</v>
@@ -7735,7 +7730,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7759,7 +7754,7 @@
         <v>80</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>134</v>
@@ -7773,10 +7768,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7799,13 +7794,13 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7832,14 +7827,14 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>404</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
       </c>
@@ -7856,7 +7851,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7894,10 +7889,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7920,13 +7915,13 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7977,7 +7972,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7989,7 +7984,7 @@
         <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>80</v>
@@ -8015,10 +8010,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8041,13 +8036,13 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8098,7 +8093,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8125,7 +8120,7 @@
         <v>80</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>80</v>
@@ -8136,10 +8131,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8168,7 +8163,7 @@
         <v>138</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>140</v>
@@ -8221,7 +8216,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8248,7 +8243,7 @@
         <v>80</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>80</v>
@@ -8259,14 +8254,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8288,10 +8283,10 @@
         <v>137</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>140</v>
@@ -8346,7 +8341,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8384,10 +8379,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8410,13 +8405,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8467,7 +8462,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8491,7 +8486,7 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>134</v>
@@ -8505,10 +8500,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8534,10 +8529,10 @@
         <v>105</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8588,7 +8583,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8626,10 +8621,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8655,10 +8650,10 @@
         <v>245</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8709,7 +8704,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8733,7 +8728,7 @@
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>134</v>
@@ -8747,10 +8742,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8776,10 +8771,10 @@
         <v>245</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8830,7 +8825,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8854,7 +8849,7 @@
         <v>80</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>134</v>
@@ -8868,10 +8863,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8894,13 +8889,13 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8927,14 +8922,14 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>431</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
       </c>
@@ -8951,7 +8946,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8975,7 +8970,7 @@
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>134</v>
@@ -8989,10 +8984,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9015,13 +9010,13 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9048,14 +9043,14 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>437</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
       </c>
@@ -9072,7 +9067,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9110,10 +9105,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9136,16 +9131,16 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9195,7 +9190,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9219,10 +9214,10 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
@@ -9233,10 +9228,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9259,13 +9254,13 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9316,7 +9311,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9343,7 +9338,7 @@
         <v>80</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9354,10 +9349,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9386,7 +9381,7 @@
         <v>138</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>140</v>
@@ -9439,7 +9434,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9466,7 +9461,7 @@
         <v>80</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9477,14 +9472,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9506,10 +9501,10 @@
         <v>137</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>140</v>
@@ -9564,7 +9559,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9602,10 +9597,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9631,10 +9626,10 @@
         <v>245</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9685,7 +9680,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9709,7 +9704,7 @@
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>240</v>
@@ -9723,10 +9718,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9749,13 +9744,13 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9806,7 +9801,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9830,10 +9825,10 @@
         <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -9844,10 +9839,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9873,10 +9868,10 @@
         <v>253</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9927,7 +9922,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9951,10 +9946,10 @@
         <v>80</v>
       </c>
       <c r="AN66" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AO66" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -9965,10 +9960,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9991,13 +9986,13 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10048,7 +10043,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10086,10 +10081,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10112,13 +10107,13 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10169,7 +10164,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10196,7 +10191,7 @@
         <v>80</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>80</v>
@@ -10207,10 +10202,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10239,7 +10234,7 @@
         <v>138</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>140</v>
@@ -10292,7 +10287,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10319,7 +10314,7 @@
         <v>80</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>80</v>
@@ -10330,14 +10325,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10359,10 +10354,10 @@
         <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>140</v>
@@ -10417,7 +10412,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10455,10 +10450,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10481,13 +10476,13 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10538,7 +10533,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10576,10 +10571,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10605,10 +10600,10 @@
         <v>276</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10659,7 +10654,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10697,10 +10692,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10723,13 +10718,13 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10756,14 +10751,14 @@
         <v>80</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y73" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="Z73" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="Z73" t="s" s="2">
-        <v>478</v>
-      </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
       </c>
@@ -10780,7 +10775,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10818,10 +10813,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10844,16 +10839,16 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10898,10 +10893,10 @@
         <v>80</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>91</v>
@@ -10939,13 +10934,13 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C75" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>80</v>
@@ -10967,16 +10962,16 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11026,7 +11021,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>91</v>
@@ -11041,7 +11036,7 @@
         <v>103</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>80</v>
@@ -11064,10 +11059,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11090,16 +11085,16 @@
         <v>80</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="M76" t="s" s="2">
-        <v>489</v>
-      </c>
       <c r="N76" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11149,7 +11144,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-VAERSImmunization-pvac2.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-pvac2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
